--- a/04_DESIGN_TABLES/DesignTable_6405.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6405.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R50"/>
+  <dimension ref="A1:S50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -565,6 +565,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1250,7 +1255,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1258,7 +1263,11 @@
           <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L31@DRIVE=1.5~1.500; HEXB@HEX=1.13~1.125; D3@BORE=0.3~0.297</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1678,7 +1687,7 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
@@ -1688,7 +1697,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>D=0.43 equals tap drill and differs from dash-expected bore 0.484 - column bleed suspected, as-printed</t>
+          <t>D=0.43 equals tap drill and differs from dash-expected bore 0.484 - column bleed suspected, as-printed | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L31@DRIVE=0.93~0.930; HEXB@HEX=1~1.000; D3@BORE=0.43~0.431</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1822,7 +1831,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -1830,7 +1839,11 @@
           <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source</t>
         </is>
       </c>
-      <c r="P20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L31@DRIVE=1.55~1.550; HEXB@HEX=1.13~1.125; D3@BORE=0.48~0.484</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2180,7 +2193,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -2188,7 +2201,11 @@
           <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source</t>
         </is>
       </c>
-      <c r="P25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L31@DRIVE=1.59~1.590; HEXB@HEX=1.38~1.375; D3@BORE=0.61~0.609</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2423,7 +2440,7 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>1.5</v>
@@ -2476,12 +2493,17 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>D=0.57 equals tap drill and differs from dash-expected bore 0.844 - column bleed suspected, as-printed | DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>D=0.57 equals tap drill and differs from dash-expected bore 0.844 - column bleed suspected, as-printed | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1790 = 0.844 (table had 0.57) | Brennan TFA TFA-p016-t01: agrees on L31@DRIVE, HEXB@HEX | 2026-10-18 rebase (A11 Q-BOREWIDE yes: cap at the port drill, report to OMi): D3@BORE stays 0.57 = the -06 female pipe tap drill; OMi 0.844 (= Brennan B DRILL) is wider than the port it runs into - the OMi D3@BORE value above is NOT applied | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L31@DRIVE 1 -&gt; 1.13</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>6405-16-06-O</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2514,7 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>1.47</v>
+        <v>1.72</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>1.5</v>
@@ -2545,12 +2567,17 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>D=0.7 equals tap drill and differs from dash-expected bore 0.844 - column bleed suspected, as-printed | DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>D=0.7 equals tap drill and differs from dash-expected bore 0.844 - column bleed suspected, as-printed | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1791 = 1.720 (table had 1.47); D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1791 = 0.844 (table had 0.7) | Brennan TFA TFA-p016-t01: agrees on L31@DRIVE, HEXB@HEX | 2026-10-18 rebase (A11 Q-BOREWIDE yes: cap at the port drill, report to OMi): D3@BORE stays 0.7 = the -08 female pipe tap drill; OMi 0.844 (= Brennan B DRILL) is wider than the port it runs into - the OMi D3@BORE value above is NOT applied</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>6405-16-08-O</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2631,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -2612,7 +2639,11 @@
           <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source</t>
         </is>
       </c>
-      <c r="P31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L31@DRIVE=1.62~1.620; HEXB@HEX=1.5~1.500; D3@BORE=0.84~0.840</t>
+        </is>
+      </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2674,7 +2705,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -2682,7 +2713,11 @@
           <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source</t>
         </is>
       </c>
-      <c r="P32" s="3" t="inlineStr"/>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L31@DRIVE=1.9~1.900; HEXB@HEX=1.63~1.625; D3@BORE=0.84~0.844</t>
+        </is>
+      </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -3041,7 +3076,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>OMi Overall Length 1.000 NOT applied (2026-09-25): exactly 1.000 like the 6410 placeholders (audit Q8); as 1.000 the pocket P1 1.14 would not fit - user decision pending</t>
+          <t>OMi Overall Length 1.000 NOT applied (2026-09-25): exactly 1.000 like the 6410 placeholders (audit Q8); as 1.000 the pocket P1 1.14 would not fit - user decision pending | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.2 (Lengths to check!E3; website file said 1.000, a filler) = the Air-Way L31 1.2 already in this row -&gt; no change; OMi and Air-Way agree on the length</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3705,24 +3740,52 @@
           <t>6405-02-02-O</t>
         </is>
       </c>
+      <c r="B47" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.062</v>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>6405-02-02-O</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>5/16-24 (ORB)</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>1/8-27 NPTF (female)</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L31@DRIVE: Brennan TFA catalog p15 table TFA-p015-t04 "6405-O MORB-FP STRAIGHT" row 6405-02-02-O col "L LGTH" = "0.950" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 640.5, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p15 6405-O drawing: L = overall, C4 HEX = body hex, B DRILL = drill from the ORB end = D3 (impact/F2b.json, certain); same-table check on today's base: 3/5 rows with an Air-Way/OMi value agree with this catalog column to rounding (2 differ, e.g. 6405-03-04-O 1.1 vs 1.2); HEXB@HEX: Brennan TFA catalog p15 table TFA-p015-t04 "6405-O MORB-FP STRAIGHT" row 6405-02-02-O col "C4 HEX" = "0.562" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 640.5, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p15 6405-O drawing: L = overall, C4 HEX = body hex, B DRILL = drill from the ORB end = D3 (impact/F2b.json, certain); same-table check on today's base: 5/5 rows with an Air-Way/OMi value agree with this catalog column to rounding; D3@BORE: Brennan TFA catalog p15 table TFA-p015-t04 "6405-O MORB-FP STRAIGHT" row 6405-02-02-O col "B DRILL" = "0.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 640.5, page verified) [Brennan = yes 2026-10-18] - bore from the ORB end; mapping: TFA p15 6405-O drawing: L = overall, C4 HEX = body hex, B DRILL = drill from the ORB end = D3 (impact/F2b.json, certain); same-table check on today's base: 5/5 rows with an Air-Way/OMi value agree with this catalog column to rounding; THDMAJ_A@DRIVE: end library gen_straight2 ORB[2] (src: 6408-02-O-SOLID row; MS51527G / MS51528D J2, Parker ORD-5700 Table 4-4) [Q-TRANSFER-ENDLIB yes] thread major; FPT_P1@DRIVE: end library gen_straight2 FPT[2] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.33, FPT_P1 0.46 = MS51503 P1 max) port depth (end detail) [Q-TRANSFER-ENDLIB yes]; TAPDRILL@BORE_A: end library gen_straight2 FPT[2] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.33, FPT_P1 0.46 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; $PRP@EndA_Thread: thread text from the part-number dash, format of the built 6405 rows; $PRP@EndB_Thread: end library gen_straight2 FPT[2] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.33, FPT_P1 0.46 = MS51503 P1 max) thread text</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L31 / hex / D3 from the Brennan TFA catalog p15 alone; ORB -02 end from the 6408-02-O-SOLID row library; tap drill = Air-Way per size (A1 yes)</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -3733,6 +3796,11 @@
       <c r="R47" t="inlineStr">
         <is>
           <t>6405-02-02-O</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -3742,24 +3810,52 @@
           <t>6405-02-04-O</t>
         </is>
       </c>
+      <c r="B48" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.062</v>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>6405-02-04-O</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>5/16-24 (ORB)</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF (female)</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L31@DRIVE: Brennan TFA catalog p15 table TFA-p015-t04 "6405-O MORB-FP STRAIGHT" row 6405-02-04-O col "L LGTH" = "1.240" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 650.6, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p15 6405-O drawing: L = overall, C4 HEX = body hex, B DRILL = drill from the ORB end = D3 (impact/F2b.json, certain); same-table check on today's base: 3/5 rows with an Air-Way/OMi value agree with this catalog column to rounding (2 differ, e.g. 6405-03-04-O 1.1 vs 1.2); HEXB@HEX: Brennan TFA catalog p15 table TFA-p015-t04 "6405-O MORB-FP STRAIGHT" row 6405-02-04-O col "C4 HEX" = "0.750" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 650.6, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p15 6405-O drawing: L = overall, C4 HEX = body hex, B DRILL = drill from the ORB end = D3 (impact/F2b.json, certain); same-table check on today's base: 5/5 rows with an Air-Way/OMi value agree with this catalog column to rounding; D3@BORE: Brennan TFA catalog p15 table TFA-p015-t04 "6405-O MORB-FP STRAIGHT" row 6405-02-04-O col "B DRILL" = "0.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 650.6, page verified) [Brennan = yes 2026-10-18] - bore from the ORB end; mapping: TFA p15 6405-O drawing: L = overall, C4 HEX = body hex, B DRILL = drill from the ORB end = D3 (impact/F2b.json, certain); same-table check on today's base: 5/5 rows with an Air-Way/OMi value agree with this catalog column to rounding; THDMAJ_A@DRIVE: end library gen_straight2 ORB[2] (src: 6408-02-O-SOLID row; MS51527G / MS51528D J2, Parker ORD-5700 Table 4-4) [Q-TRANSFER-ENDLIB yes] thread major; FPT_P1@DRIVE: end library gen_straight2 FPT[4] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.43, FPT_P1 0.67 = MS51503 P1 max) port depth (end detail) [Q-TRANSFER-ENDLIB yes]; TAPDRILL@BORE_A: end library gen_straight2 FPT[4] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.43, FPT_P1 0.67 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; $PRP@EndA_Thread: thread text from the part-number dash, format of the built 6405 rows; $PRP@EndB_Thread: end library gen_straight2 FPT[4] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.43, FPT_P1 0.67 = MS51503 P1 max) thread text</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L31 / hex / D3 from the Brennan TFA catalog p15 alone; ORB -02 end from the 6408-02-O-SOLID row library; tap drill = Air-Way per size (A1 yes)</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -3770,6 +3866,11 @@
       <c r="R48" t="inlineStr">
         <is>
           <t>6405-02-04-O</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_6405.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6405.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.88</v>
@@ -836,10 +836,14 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1766 Overall Length = 1.350 (table had 1.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1766 Overall Length = 1.350 (table had 1.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.25 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.35) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.35 -&gt; Air-Way 1.25</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -858,7 +862,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.63</v>
@@ -906,10 +910,14 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1767 Overall Length = 0.990 (table had 0.94) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1767 Overall Length = 0.990 (table had 0.94) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 0.94 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.99) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 0.99 -&gt; Air-Way 0.94</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -928,7 +936,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0.75</v>
@@ -976,10 +984,14 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1768 Overall Length = 1.200 (table had 1.15) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1768 Overall Length = 1.200 (table had 1.15) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.15 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.2) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.2 -&gt; Air-Way 1.15</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -998,7 +1010,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1.02</v>
+        <v>0.73</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.6899999999999999</v>
@@ -1022,7 +1034,7 @@
         <v>0.33</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.297</v>
+        <v>0.33</v>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
@@ -1046,12 +1058,12 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1769 Overall Length = 1.020 (table had 0.73); D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1769 Side 1 ID = 0.297 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1769 Overall Length = 1.020 (table had 0.73); D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1769 Side 1 ID = 0.297 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 0.73 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.02) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D3@BORE: Air-Way 0.33 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.297) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>D=0.33 equals tap drill and differs from dash-expected bore 0.297 - column bleed suspected, as-printed</t>
+          <t>D=0.33 equals tap drill and differs from dash-expected bore 0.297 - column bleed suspected, as-printed | 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.02 -&gt; Air-Way 0.73 | 2026-10-20 Air-Way first: D3@BORE OMi/Brennan 0.297 -&gt; Air-Way 0.33</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1072,10 +1084,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.5625</v>
@@ -1120,10 +1132,14 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1770 Overall Length = 1.090 (table had 1.18); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1770 Hex Flat = 0.750 (table had 0.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr"/>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1770 Overall Length = 1.090 (table had 1.18); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1770 Hex Flat = 0.750 (table had 0.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.18 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.09) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; HEXB@HEX: Air-Way 0.69 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.75) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.09 -&gt; Air-Way 1.18 | 2026-10-20 Air-Way first: HEXB@HEX OMi/Brennan 0.75 -&gt; Air-Way 0.69</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1142,7 +1158,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>0.88</v>
@@ -1190,10 +1206,14 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1771 Overall Length = 1.330 (table had 1.31) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1771 Overall Length = 1.330 (table had 1.31) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.31 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.33) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.33 -&gt; Air-Way 1.31</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1310,7 +1330,7 @@
         <v>0.33</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.315</v>
+        <v>0.33</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
@@ -1334,12 +1354,12 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1773 Side 1 ID = 0.315 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1773 Side 1 ID = 0.315 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D3@BORE: Air-Way 0.33 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.315) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>D=0.33 equals tap drill and differs from dash-expected bore 0.391 - column bleed suspected, as-printed</t>
+          <t>D=0.33 equals tap drill and differs from dash-expected bore 0.391 - column bleed suspected, as-printed | 2026-10-20 Air-Way first: D3@BORE OMi/Brennan 0.315 -&gt; Air-Way 0.33</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1384,7 +1404,7 @@
         <v>0.43</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.391</v>
+        <v>0.43</v>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
@@ -1408,12 +1428,12 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1774 Side 1 ID = 0.391 (table had 0.43) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1774 Side 1 ID = 0.391 (table had 0.43) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D3@BORE: Air-Way 0.43 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.391) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>D=0.43 equals tap drill and differs from dash-expected bore 0.391 - column bleed suspected, as-printed</t>
+          <t>D=0.43 equals tap drill and differs from dash-expected bore 0.391 - column bleed suspected, as-printed | 2026-10-20 Air-Way first: D3@BORE OMi/Brennan 0.391 -&gt; Air-Way 0.43</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1434,7 +1454,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0.88</v>
@@ -1482,10 +1502,14 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1775 Overall Length = 1.280 (table had 1.26) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr"/>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1775 Overall Length = 1.280 (table had 1.26) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.26 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.28) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.28 -&gt; Air-Way 1.26</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1504,7 +1528,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>1.13</v>
@@ -1552,10 +1576,14 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1776 Overall Length = 1.470 (table had 1.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr"/>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1776 Overall Length = 1.470 (table had 1.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.63 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.47) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.47 -&gt; Air-Way 1.63</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1574,7 +1602,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>1.38</v>
@@ -1622,10 +1650,14 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1777 Overall Length = 1.780 (table had 1.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr"/>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1777 Overall Length = 1.780 (table had 1.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.63 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.78) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.78 -&gt; Air-Way 1.63</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1718,7 +1750,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>1</v>
@@ -1766,10 +1798,14 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1780 Overall Length = 1.400 (table had 1.28) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr"/>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1780 Overall Length = 1.400 (table had 1.28) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.28 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.4) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.4 -&gt; Air-Way 1.28</t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1862,7 +1898,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>1.38</v>
@@ -1910,10 +1946,14 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1782 Overall Length = 1.710 (table had 1.64) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr"/>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1782 Overall Length = 1.710 (table had 1.64) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.64 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.71) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.71 -&gt; Air-Way 1.64</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2006,7 +2046,7 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>1.49</v>
+        <v>1.09</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>1.25</v>
@@ -2054,12 +2094,12 @@
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1784 Overall Length = 1.490 (table had 1.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1784 Overall Length = 1.490 (table had 1.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.09 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.49) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>D=0.57 equals tap drill and differs from dash-expected bore 0.609 - column bleed suspected, as-printed | OMi Side 1 ID 0.609 NOT applied (2026-09-25): wider than the female port it runs into (pocket (tap drill) 0.57); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending</t>
+          <t>D=0.57 equals tap drill and differs from dash-expected bore 0.609 - column bleed suspected, as-printed | OMi Side 1 ID 0.609 NOT applied (2026-09-25): wider than the female port it runs into (pocket (tap drill) 0.57); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.49 -&gt; Air-Way 1.09</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2080,7 +2120,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>1.25</v>
@@ -2128,10 +2168,14 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1785 Overall Length = 1.410 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr"/>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1785 Overall Length = 1.410 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.5 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.41) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.41 -&gt; Air-Way 1.5</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2224,7 +2268,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>1.63</v>
@@ -2272,10 +2316,14 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1787 Overall Length = 2.030 (table had 1.95) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr"/>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1787 Overall Length = 2.030 (table had 1.95) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.95 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.03) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 2.03 -&gt; Air-Way 1.95</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2294,7 +2342,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="C27" s="5" t="n">
         <v>1.38</v>
@@ -2340,12 +2388,12 @@
       </c>
       <c r="O27" s="5" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1788 Overall Length = 1.780 (table had 1.6) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1788 Overall Length = 1.780 (table had 1.6) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.6 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.78) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="P27" s="5" t="inlineStr">
         <is>
-          <t>ORB -14 groove width unmeasured</t>
+          <t>ORB -14 groove width unmeasured | 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.78 -&gt; Air-Way 1.6</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2366,7 +2414,7 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>1.5</v>
@@ -2414,12 +2462,12 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1789 Overall Length = 1.140 (table had 1.12) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1789 Overall Length = 1.140 (table had 1.12) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.12 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.14) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>D=0.43 equals tap drill and differs from dash-expected bore 0.844 - column bleed suspected, as-printed</t>
+          <t>D=0.43 equals tap drill and differs from dash-expected bore 0.844 - column bleed suspected, as-printed | 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.14 -&gt; Air-Way 1.12</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2440,7 +2488,7 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>1.5</v>
@@ -2488,12 +2536,12 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: Air-Way 1 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.13) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>D=0.57 equals tap drill and differs from dash-expected bore 0.844 - column bleed suspected, as-printed | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1790 = 0.844 (table had 0.57) | Brennan TFA TFA-p016-t01: agrees on L31@DRIVE, HEXB@HEX | 2026-10-18 rebase (A11 Q-BOREWIDE yes: cap at the port drill, report to OMi): D3@BORE stays 0.57 = the -06 female pipe tap drill; OMi 0.844 (= Brennan B DRILL) is wider than the port it runs into - the OMi D3@BORE value above is NOT applied | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L31@DRIVE 1 -&gt; 1.13</t>
+          <t>D=0.57 equals tap drill and differs from dash-expected bore 0.844 - column bleed suspected, as-printed | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1790 = 0.844 (table had 0.57) | Brennan TFA TFA-p016-t01: agrees on L31@DRIVE, HEXB@HEX | 2026-10-18 rebase (A11 Q-BOREWIDE yes: cap at the port drill, report to OMi): D3@BORE stays 0.57 = the -06 female pipe tap drill; OMi 0.844 (= Brennan B DRILL) is wider than the port it runs into - the OMi D3@BORE value above is NOT applied | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L31@DRIVE 1 -&gt; 1.13 | 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.13 -&gt; Air-Way 1</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2514,7 +2562,7 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>1.5</v>
@@ -2562,12 +2610,12 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: Air-Way 1.47 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.72) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>D=0.7 equals tap drill and differs from dash-expected bore 0.844 - column bleed suspected, as-printed | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1791 = 1.720 (table had 1.47); D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1791 = 0.844 (table had 0.7) | Brennan TFA TFA-p016-t01: agrees on L31@DRIVE, HEXB@HEX | 2026-10-18 rebase (A11 Q-BOREWIDE yes: cap at the port drill, report to OMi): D3@BORE stays 0.7 = the -08 female pipe tap drill; OMi 0.844 (= Brennan B DRILL) is wider than the port it runs into - the OMi D3@BORE value above is NOT applied</t>
+          <t>D=0.7 equals tap drill and differs from dash-expected bore 0.844 - column bleed suspected, as-printed | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1791 = 1.720 (table had 1.47); D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1791 = 0.844 (table had 0.7) | Brennan TFA TFA-p016-t01: agrees on L31@DRIVE, HEXB@HEX | 2026-10-18 rebase (A11 Q-BOREWIDE yes: cap at the port drill, report to OMi): D3@BORE stays 0.7 = the -08 female pipe tap drill; OMi 0.844 (= Brennan B DRILL) is wider than the port it runs into - the OMi D3@BORE value above is NOT applied | 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.72 -&gt; Air-Way 1.47</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2736,7 +2784,7 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>2.27</v>
+        <v>2.09</v>
       </c>
       <c r="C33" s="3" t="n">
         <v>2</v>
@@ -2784,10 +2832,14 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1794 Overall Length = 2.270 (table had 2.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr"/>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1794 Overall Length = 2.270 (table had 2.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 2.09 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.27) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 2.27 -&gt; Air-Way 2.09</t>
+        </is>
+      </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2899,7 +2951,7 @@
         <v>0.7</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.649</v>
+        <v>0.7</v>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
@@ -2923,12 +2975,12 @@
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1796 Side 1 ID = 0.649 (table had 0.7) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1796 Side 1 ID = 0.649 (table had 0.7) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D3@BORE: Air-Way 0.7 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.649) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>D=0.7 equals tap drill and differs from dash-expected bore 1.078 - column bleed suspected, as-printed</t>
+          <t>D=0.7 equals tap drill and differs from dash-expected bore 1.078 - column bleed suspected, as-printed | 2026-10-20 Air-Way first: D3@BORE OMi/Brennan 0.649 -&gt; Air-Way 0.7</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -2973,7 +3025,7 @@
         <v>0.91</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>0.854</v>
+        <v>0.91</v>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
@@ -2997,12 +3049,12 @@
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1797 Side 1 ID = 0.854 (table had 0.91) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1797 Side 1 ID = 0.854 (table had 0.91) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D3@BORE: Air-Way 0.91 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.854) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>D=0.91 equals tap drill and differs from dash-expected bore 1.078 - column bleed suspected, as-printed</t>
+          <t>D=0.91 equals tap drill and differs from dash-expected bore 1.078 - column bleed suspected, as-printed | 2026-10-20 Air-Way first: D3@BORE OMi/Brennan 0.854 -&gt; Air-Way 0.91</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3097,7 +3149,7 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>2</v>
@@ -3145,10 +3197,14 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1799 Overall Length = 1.970 (table had 1.95) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr"/>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1799 Overall Length = 1.970 (table had 1.95) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.95 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.97) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.97 -&gt; Air-Way 1.95</t>
+        </is>
+      </c>
       <c r="Q38" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -3167,7 +3223,7 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>2.38</v>
@@ -3215,10 +3271,14 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1800 Overall Length = 2.300 (table had 2.27) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr"/>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1800 Overall Length = 2.300 (table had 2.27) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 2.27 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.3) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 2.3 -&gt; Air-Way 2.27</t>
+        </is>
+      </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -3237,7 +3297,7 @@
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="C40" s="4" t="n">
         <v>2.13</v>
@@ -3285,12 +3345,12 @@
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1801 Overall Length = 1.270 (table had 1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1801 Overall Length = 1.270 (table had 1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.27) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>D=0.91 equals tap drill and differs from dash-expected bore 1.312 - column bleed suspected, as-printed</t>
+          <t>D=0.91 equals tap drill and differs from dash-expected bore 1.312 - column bleed suspected, as-printed | 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.27 -&gt; Air-Way 1</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -3335,7 +3395,7 @@
         <v>1.14</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
@@ -3359,12 +3419,12 @@
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1802 Overall Length = 1.750 (table had 1); D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1802 Side 1 ID = 1.080 (table had 1.14) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>[BRENNAN-CELL 2026-10-20: L31@DRIVE] ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1802 Overall Length = 1.750 (table had 1); D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1802 Side 1 ID = 1.080 (table had 1.14) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D3@BORE: Air-Way 1.14 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.08) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L31@DRIVE: Brennan TFA catalog p16 table TFA-p016-t01 "MORB-FP STRAIGHT" row 6405-24-16-O col "L LGTH" = 1.75 [user 2026-10-20 Q1: Air-Way value cannot be built -&gt; Brennan]</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>D=1.14 equals tap drill and differs from dash-expected bore 1.312 - column bleed suspected, as-printed</t>
+          <t>D=1.14 equals tap drill and differs from dash-expected bore 1.312 - column bleed suspected, as-printed | 2026-10-20 Air-Way first: D3@BORE OMi/Brennan 1.08 -&gt; Air-Way 1.14 | 2026-10-20 L31@DRIVE = Brennan 1.75 (Air-Way 1.0 cannot be built: Air-Way L 1.00 &lt; the 1-NPTF pocket depth 1.14: no room for a bore (generator BLOCKED))</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3375,6 +3435,11 @@
       <c r="R41" t="inlineStr">
         <is>
           <t>6405-24-16-O</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3450,7 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>2.13</v>
@@ -3433,10 +3498,14 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1803 Overall Length = 2.160 (table had 1.85) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr"/>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1803 Overall Length = 2.160 (table had 1.85) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.85 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.16) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 2.16 -&gt; Air-Way 1.85</t>
+        </is>
+      </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -3455,7 +3524,7 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>2.38</v>
@@ -3503,10 +3572,14 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1804 Overall Length = 2.160 (table had 2) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr"/>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1804 Overall Length = 2.160 (table had 2) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 2 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.16) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 2.16 -&gt; Air-Way 2</t>
+        </is>
+      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -3525,7 +3598,7 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="C44" s="5" t="n">
         <v>2.75</v>
@@ -3571,12 +3644,12 @@
       </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1806 Overall Length = 2.000 (table had 1.43) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1806 Overall Length = 2.000 (table had 1.43) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.43 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="P44" s="5" t="inlineStr">
         <is>
-          <t>ORB -32 groove width unmeasured; D=1.48 equals tap drill and differs from dash-expected bore 1.781 - column bleed suspected, as-printed | OMi Side 1 ID 1.781 NOT applied (2026-09-25): wider than the female port it runs into (pocket (tap drill) 1.48); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending</t>
+          <t>ORB -32 groove width unmeasured; D=1.48 equals tap drill and differs from dash-expected bore 1.781 - column bleed suspected, as-printed | OMi Side 1 ID 1.781 NOT applied (2026-09-25): wider than the female port it runs into (pocket (tap drill) 1.48); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 2 -&gt; Air-Way 1.43</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -3597,7 +3670,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="C45" s="5" t="n">
         <v>2.75</v>
@@ -3643,12 +3716,12 @@
       </c>
       <c r="O45" s="5" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1807 Overall Length = 2.000 (table had 1.43) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1807 Overall Length = 2.000 (table had 1.43) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.43 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="P45" s="5" t="inlineStr">
         <is>
-          <t>ORB -32 groove width unmeasured | OMi Side 1 ID 1.734 NOT applied (2026-09-25): wider than the female port it runs into (pocket (tap drill) 1.72); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending</t>
+          <t>ORB -32 groove width unmeasured | OMi Side 1 ID 1.734 NOT applied (2026-09-25): wider than the female port it runs into (pocket (tap drill) 1.72); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 2 -&gt; Air-Way 1.43</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -3669,7 +3742,7 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="C46" s="5" t="n">
         <v>2.88</v>
@@ -3715,12 +3788,12 @@
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1808 Overall Length = 2.240 (table had 2.23) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1808 Overall Length = 2.240 (table had 2.23) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 2.23 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.24) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="P46" s="5" t="inlineStr">
         <is>
-          <t>ORB -32 groove width unmeasured</t>
+          <t>ORB -32 groove width unmeasured | 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 2.24 -&gt; Air-Way 2.23</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6405.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6405.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3990,24 +3990,58 @@
           <t>6405-32-16-O</t>
         </is>
       </c>
+      <c r="B50" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.381</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.08</v>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>6405-32-16-O</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (ORB)</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L31 / hex / D3 = OMi WebsitePartsInfo2026.xlsx Items row 1805; tap drill 1.14 = Air-Way -16 (A1); -32 ORB end from the end library (ORB[32]: 6408-32-O-SOLID row + groove width 0.125 measured on the Brennan 6400-32-32-O STEP, A18 - ORB_GRVW left empty on purpose, the generator applies the library value); FPT_P1 from the 2405 end library</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): filled from OMi Items row 1805 + A1 tap drill; D3 OMi 1.080 vs Brennan TFA p16 B DRILL 1.156 - OMi kept (source order), tell the user</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -4018,6 +4052,11 @@
       <c r="R50" t="inlineStr">
         <is>
           <t>6405-32-16-O</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
